--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.695060994500068</v>
+        <v>1.575447411606261</v>
       </c>
       <c r="D2" t="n">
-        <v>10.07693794895724</v>
+        <v>1.637502416705552</v>
       </c>
       <c r="E2" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F2" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.49426740413319</v>
+        <v>3.817818453171644</v>
       </c>
       <c r="D3" t="n">
-        <v>24.86846794907199</v>
+        <v>4.041126041724199</v>
       </c>
       <c r="E3" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F3" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.49556443670382</v>
+        <v>6.580529220964372</v>
       </c>
       <c r="D4" t="n">
-        <v>41.10614155508379</v>
+        <v>6.679748002701117</v>
       </c>
       <c r="E4" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F4" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.22337441584905</v>
+        <v>4.748798342575471</v>
       </c>
       <c r="D5" t="n">
-        <v>29.13632528112033</v>
+        <v>4.734652858182054</v>
       </c>
       <c r="E5" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F5" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.871789012470906</v>
+        <v>1.441665714526522</v>
       </c>
       <c r="D6" t="n">
-        <v>11.23099777189538</v>
+        <v>1.825037137932999</v>
       </c>
       <c r="E6" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F6" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.421319295565</v>
+        <v>6.405964385529312</v>
       </c>
       <c r="D7" t="n">
-        <v>39.21058020111163</v>
+        <v>6.37171928268064</v>
       </c>
       <c r="E7" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F7" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.60085636778742</v>
+        <v>6.597639159765455</v>
       </c>
       <c r="D8" t="n">
-        <v>40.18411241359655</v>
+        <v>6.52991826720944</v>
       </c>
       <c r="E8" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F8" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.53770534285098</v>
+        <v>3.987377118213285</v>
       </c>
       <c r="D9" t="n">
-        <v>23.65754766388265</v>
+        <v>3.844351495380931</v>
       </c>
       <c r="E9" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F9" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.64553718521767</v>
+        <v>6.442399792597872</v>
       </c>
       <c r="D10" t="n">
-        <v>39.36577284445507</v>
+        <v>6.396938087223949</v>
       </c>
       <c r="E10" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F10" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.79535880804303</v>
+        <v>4.029245806306992</v>
       </c>
       <c r="D11" t="n">
-        <v>12.61942946412396</v>
+        <v>2.050657287920144</v>
       </c>
       <c r="E11" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F11" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.74410278440295</v>
+        <v>5.645916702465479</v>
       </c>
       <c r="D12" t="n">
-        <v>24.28687864599869</v>
+        <v>3.946617779974787</v>
       </c>
       <c r="E12" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F12" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.62337693279679</v>
+        <v>4.48879875157948</v>
       </c>
       <c r="D13" t="n">
-        <v>17.43388082491343</v>
+        <v>2.833005634048432</v>
       </c>
       <c r="E13" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F13" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.65058379907228</v>
+        <v>2.380719867349246</v>
       </c>
       <c r="D14" t="n">
-        <v>4.40279968448809</v>
+        <v>0.7154549487293147</v>
       </c>
       <c r="E14" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F14" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>47.57965701749767</v>
+        <v>7.731694265343372</v>
       </c>
       <c r="D15" t="n">
-        <v>50.08359474042246</v>
+        <v>8.138584145318651</v>
       </c>
       <c r="E15" t="n">
-        <v>11.71205260452378</v>
+        <v>1.903208548235115</v>
       </c>
       <c r="F15" t="n">
-        <v>13.55325999739235</v>
+        <v>2.202404749576257</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
